--- a/reports/jobs_2026-09-07.xlsx
+++ b/reports/jobs_2026-09-07.xlsx
@@ -11,7 +11,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Errors" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Jobs'!$A$1:$I$78</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Jobs'!$A$1:$I$79</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -456,7 +456,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I78"/>
+  <dimension ref="A1:I79"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -520,27 +520,27 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Okta India</t>
+          <t>Continental India</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>SRE Operations Engineer</t>
+          <t xml:space="preserve">IT B2B/EDI Developer </t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>DevOps / SRE</t>
+          <t>Software (General)</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>1+ years</t>
+          <t>Not specified</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Bengaluru, India</t>
+          <t>Bengaluru, in</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -550,12 +550,12 @@
       </c>
       <c r="G2" s="3" t="inlineStr">
         <is>
-          <t>https://www.okta.com/company/careers/opportunity/8003315?gh_jid=8003315</t>
+          <t>https://api.smartrecruiters.com/v1/companies/continental/postings/744000147905349</t>
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>https://boards.greenhouse.io/okta</t>
+          <t>https://careers.smartrecruiters.com/continental</t>
         </is>
       </c>
       <c r="I2" s="2" t="inlineStr">
@@ -565,57 +565,57 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="4" t="inlineStr">
-        <is>
-          <t>Agnikul Cosmos</t>
-        </is>
-      </c>
-      <c r="B3" s="4" t="inlineStr">
-        <is>
-          <t>Careers Inquiries humancapital@agnikul.in</t>
-        </is>
-      </c>
-      <c r="C3" s="4" t="inlineStr">
-        <is>
-          <t>Software (General)</t>
-        </is>
-      </c>
-      <c r="D3" s="4" t="inlineStr">
-        <is>
-          <t>Not specified</t>
-        </is>
-      </c>
-      <c r="E3" s="4" t="inlineStr"/>
-      <c r="F3" s="4" t="inlineStr">
-        <is>
-          <t>2026-09-07</t>
-        </is>
-      </c>
-      <c r="G3" s="5" t="inlineStr">
-        <is>
-          <t>mailto:%20humancapital@agnikul.in</t>
-        </is>
-      </c>
-      <c r="H3" s="4" t="inlineStr">
-        <is>
-          <t>https://agnikul.in/careers</t>
-        </is>
-      </c>
-      <c r="I3" s="4" t="inlineStr">
-        <is>
-          <t>No</t>
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>Fractal Analytics</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>Snowflake Data Engineer</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t>Data</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="E3" s="2" t="inlineStr"/>
+      <c r="F3" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="G3" s="3" t="inlineStr">
+        <is>
+          <t>https://fractal.ai/en-US/Careers/job/London/Snowflake-Data-Engineer_SR-45644</t>
+        </is>
+      </c>
+      <c r="H3" s="2" t="inlineStr">
+        <is>
+          <t>https://fractal.ai/careers/</t>
+        </is>
+      </c>
+      <c r="I3" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="4" t="inlineStr">
         <is>
-          <t>Agoda India</t>
+          <t>Agnikul Cosmos</t>
         </is>
       </c>
       <c r="B4" s="4" t="inlineStr">
         <is>
-          <t>Chiang Mai 1 available jobs</t>
+          <t>Careers Inquiries humancapital@agnikul.in</t>
         </is>
       </c>
       <c r="C4" s="4" t="inlineStr">
@@ -628,11 +628,7 @@
           <t>Not specified</t>
         </is>
       </c>
-      <c r="E4" s="4" t="inlineStr">
-        <is>
-          <t>Mumbai 0 available jobs Ok</t>
-        </is>
-      </c>
+      <c r="E4" s="4" t="inlineStr"/>
       <c r="F4" s="4" t="inlineStr">
         <is>
           <t>2026-09-07</t>
@@ -640,12 +636,12 @@
       </c>
       <c r="G4" s="5" t="inlineStr">
         <is>
-          <t>https://careersatagoda.com/location/chiang-mai/</t>
+          <t>mailto:%20humancapital@agnikul.in</t>
         </is>
       </c>
       <c r="H4" s="4" t="inlineStr">
         <is>
-          <t>https://careersatagoda.com/</t>
+          <t>https://agnikul.in/careers</t>
         </is>
       </c>
       <c r="I4" s="4" t="inlineStr">
@@ -662,7 +658,7 @@
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>Dubai 0 available jobs</t>
+          <t>Chiang Mai 1 available jobs</t>
         </is>
       </c>
       <c r="C5" s="4" t="inlineStr">
@@ -687,7 +683,7 @@
       </c>
       <c r="G5" s="5" t="inlineStr">
         <is>
-          <t>https://careersatagoda.com/location/dubai/</t>
+          <t>https://careersatagoda.com/location/chiang-mai/</t>
         </is>
       </c>
       <c r="H5" s="4" t="inlineStr">
@@ -709,7 +705,7 @@
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>Mumbai 0 available jobs</t>
+          <t>Dubai 0 available jobs</t>
         </is>
       </c>
       <c r="C6" s="4" t="inlineStr">
@@ -734,7 +730,7 @@
       </c>
       <c r="G6" s="5" t="inlineStr">
         <is>
-          <t>https://careersatagoda.com/location/mumbai/</t>
+          <t>https://careersatagoda.com/location/dubai/</t>
         </is>
       </c>
       <c r="H6" s="4" t="inlineStr">
@@ -756,7 +752,7 @@
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>Shanghai 0 available jobs</t>
+          <t>Mumbai 0 available jobs</t>
         </is>
       </c>
       <c r="C7" s="4" t="inlineStr">
@@ -781,7 +777,7 @@
       </c>
       <c r="G7" s="5" t="inlineStr">
         <is>
-          <t>https://careersatagoda.com/location/shanghai/</t>
+          <t>https://careersatagoda.com/location/mumbai/</t>
         </is>
       </c>
       <c r="H7" s="4" t="inlineStr">
@@ -803,7 +799,7 @@
       </c>
       <c r="B8" s="4" t="inlineStr">
         <is>
-          <t>Engineering &amp; Technology</t>
+          <t>Shanghai 0 available jobs</t>
         </is>
       </c>
       <c r="C8" s="4" t="inlineStr">
@@ -816,7 +812,11 @@
           <t>Not specified</t>
         </is>
       </c>
-      <c r="E8" s="4" t="inlineStr"/>
+      <c r="E8" s="4" t="inlineStr">
+        <is>
+          <t>Mumbai 0 available jobs Ok</t>
+        </is>
+      </c>
       <c r="F8" s="4" t="inlineStr">
         <is>
           <t>2026-09-07</t>
@@ -824,7 +824,7 @@
       </c>
       <c r="G8" s="5" t="inlineStr">
         <is>
-          <t>https://careersatagoda.com/department/technology/</t>
+          <t>https://careersatagoda.com/location/shanghai/</t>
         </is>
       </c>
       <c r="H8" s="4" t="inlineStr">
@@ -846,7 +846,7 @@
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>Mumbai jobs</t>
+          <t>Engineering &amp; Technology</t>
         </is>
       </c>
       <c r="C9" s="4" t="inlineStr">
@@ -859,11 +859,7 @@
           <t>Not specified</t>
         </is>
       </c>
-      <c r="E9" s="4" t="inlineStr">
-        <is>
-          <t>Mumbai jobs Yokohama jobs</t>
-        </is>
-      </c>
+      <c r="E9" s="4" t="inlineStr"/>
       <c r="F9" s="4" t="inlineStr">
         <is>
           <t>2026-09-07</t>
@@ -871,7 +867,7 @@
       </c>
       <c r="G9" s="5" t="inlineStr">
         <is>
-          <t>https://careersatagoda.com/location/mumbai-india/</t>
+          <t>https://careersatagoda.com/department/technology/</t>
         </is>
       </c>
       <c r="H9" s="4" t="inlineStr">
@@ -893,12 +889,12 @@
       </c>
       <c r="B10" s="4" t="inlineStr">
         <is>
-          <t>Backend Developer Jobs</t>
+          <t>Mumbai jobs</t>
         </is>
       </c>
       <c r="C10" s="4" t="inlineStr">
         <is>
-          <t>Backend</t>
+          <t>Software (General)</t>
         </is>
       </c>
       <c r="D10" s="4" t="inlineStr">
@@ -906,7 +902,11 @@
           <t>Not specified</t>
         </is>
       </c>
-      <c r="E10" s="4" t="inlineStr"/>
+      <c r="E10" s="4" t="inlineStr">
+        <is>
+          <t>Mumbai jobs Yokohama jobs</t>
+        </is>
+      </c>
       <c r="F10" s="4" t="inlineStr">
         <is>
           <t>2026-09-07</t>
@@ -914,7 +914,7 @@
       </c>
       <c r="G10" s="5" t="inlineStr">
         <is>
-          <t>https://careersatagoda.com/vacancies/?search=back%20end</t>
+          <t>https://careersatagoda.com/location/mumbai-india/</t>
         </is>
       </c>
       <c r="H10" s="4" t="inlineStr">
@@ -936,12 +936,12 @@
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>Full Stack Developer Jobs</t>
+          <t>Backend Developer Jobs</t>
         </is>
       </c>
       <c r="C11" s="4" t="inlineStr">
         <is>
-          <t>Full Stack</t>
+          <t>Backend</t>
         </is>
       </c>
       <c r="D11" s="4" t="inlineStr">
@@ -957,7 +957,7 @@
       </c>
       <c r="G11" s="5" t="inlineStr">
         <is>
-          <t>https://careersatagoda.com/vacancies/?search=Full%20Stack</t>
+          <t>https://careersatagoda.com/vacancies/?search=back%20end</t>
         </is>
       </c>
       <c r="H11" s="4" t="inlineStr">
@@ -979,12 +979,12 @@
       </c>
       <c r="B12" s="4" t="inlineStr">
         <is>
-          <t>Software Engineer Jobs</t>
+          <t>Full Stack Developer Jobs</t>
         </is>
       </c>
       <c r="C12" s="4" t="inlineStr">
         <is>
-          <t>Software (General)</t>
+          <t>Full Stack</t>
         </is>
       </c>
       <c r="D12" s="4" t="inlineStr">
@@ -1000,7 +1000,7 @@
       </c>
       <c r="G12" s="5" t="inlineStr">
         <is>
-          <t>https://careersatagoda.com/vacancies/?search=software%20engineer</t>
+          <t>https://careersatagoda.com/vacancies/?search=Full%20Stack</t>
         </is>
       </c>
       <c r="H12" s="4" t="inlineStr">
@@ -1017,12 +1017,12 @@
     <row r="13">
       <c r="A13" s="4" t="inlineStr">
         <is>
-          <t>Arm India</t>
+          <t>Agoda India</t>
         </is>
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>Theorem Proving Engineer</t>
+          <t>Software Engineer Jobs</t>
         </is>
       </c>
       <c r="C13" s="4" t="inlineStr">
@@ -1043,12 +1043,12 @@
       </c>
       <c r="G13" s="5" t="inlineStr">
         <is>
-          <t>https://careers.arm.com/job/austin/theorem-proving-engineer/33099/97584421536</t>
+          <t>https://careersatagoda.com/vacancies/?search=software%20engineer</t>
         </is>
       </c>
       <c r="H13" s="4" t="inlineStr">
         <is>
-          <t>https://careers.arm.com/</t>
+          <t>https://careersatagoda.com/</t>
         </is>
       </c>
       <c r="I13" s="4" t="inlineStr">
@@ -1060,17 +1060,17 @@
     <row r="14">
       <c r="A14" s="4" t="inlineStr">
         <is>
-          <t>Arm India</t>
+          <t>Atlan</t>
         </is>
       </c>
       <c r="B14" s="4" t="inlineStr">
         <is>
-          <t>Embedded Compiler Engineer (Machine Learning)</t>
+          <t>Field Security Engineer</t>
         </is>
       </c>
       <c r="C14" s="4" t="inlineStr">
         <is>
-          <t>AI / ML</t>
+          <t>Software (General)</t>
         </is>
       </c>
       <c r="D14" s="4" t="inlineStr">
@@ -1078,7 +1078,11 @@
           <t>Not specified</t>
         </is>
       </c>
-      <c r="E14" s="4" t="inlineStr"/>
+      <c r="E14" s="4" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
       <c r="F14" s="4" t="inlineStr">
         <is>
           <t>2026-09-07</t>
@@ -1086,12 +1090,12 @@
       </c>
       <c r="G14" s="5" t="inlineStr">
         <is>
-          <t>https://careers.arm.com/job/lund/embedded-compiler-engineer-machine-learning/33099/94847322016</t>
+          <t>https://jobs.ashbyhq.com/atlan/b2b880ed-63cd-4f56-8313-87f143fa9807</t>
         </is>
       </c>
       <c r="H14" s="4" t="inlineStr">
         <is>
-          <t>https://careers.arm.com/</t>
+          <t>https://jobs.ashbyhq.com/atlan</t>
         </is>
       </c>
       <c r="I14" s="4" t="inlineStr">
@@ -1103,12 +1107,12 @@
     <row r="15">
       <c r="A15" s="4" t="inlineStr">
         <is>
-          <t>Atlan</t>
+          <t>Atlassian India</t>
         </is>
       </c>
       <c r="B15" s="4" t="inlineStr">
         <is>
-          <t>Field Security Engineer</t>
+          <t>Engineering</t>
         </is>
       </c>
       <c r="C15" s="4" t="inlineStr">
@@ -1121,11 +1125,7 @@
           <t>Not specified</t>
         </is>
       </c>
-      <c r="E15" s="4" t="inlineStr">
-        <is>
-          <t>India</t>
-        </is>
-      </c>
+      <c r="E15" s="4" t="inlineStr"/>
       <c r="F15" s="4" t="inlineStr">
         <is>
           <t>2026-09-07</t>
@@ -1133,12 +1133,12 @@
       </c>
       <c r="G15" s="5" t="inlineStr">
         <is>
-          <t>https://jobs.ashbyhq.com/atlan/b2b880ed-63cd-4f56-8313-87f143fa9807</t>
+          <t>https://www.atlassian.com/company/careers/engineering</t>
         </is>
       </c>
       <c r="H15" s="4" t="inlineStr">
         <is>
-          <t>https://jobs.ashbyhq.com/atlan</t>
+          <t>https://www.atlassian.com/company/careers/all-jobs</t>
         </is>
       </c>
       <c r="I15" s="4" t="inlineStr">
@@ -1155,12 +1155,12 @@
       </c>
       <c r="B16" s="4" t="inlineStr">
         <is>
-          <t>Engineering</t>
+          <t>AI and Machine Learning</t>
         </is>
       </c>
       <c r="C16" s="4" t="inlineStr">
         <is>
-          <t>Software (General)</t>
+          <t>AI / ML</t>
         </is>
       </c>
       <c r="D16" s="4" t="inlineStr">
@@ -1176,7 +1176,7 @@
       </c>
       <c r="G16" s="5" t="inlineStr">
         <is>
-          <t>https://www.atlassian.com/company/careers/engineering</t>
+          <t>https://www.atlassian.com/company/careers/engineering/ai</t>
         </is>
       </c>
       <c r="H16" s="4" t="inlineStr">
@@ -1193,12 +1193,12 @@
     <row r="17">
       <c r="A17" s="4" t="inlineStr">
         <is>
-          <t>Atlassian India</t>
+          <t>Databricks India</t>
         </is>
       </c>
       <c r="B17" s="4" t="inlineStr">
         <is>
-          <t>AI and Machine Learning</t>
+          <t>AI Engineer - FDE (Forward Deployed Engineer)</t>
         </is>
       </c>
       <c r="C17" s="4" t="inlineStr">
@@ -1211,7 +1211,11 @@
           <t>Not specified</t>
         </is>
       </c>
-      <c r="E17" s="4" t="inlineStr"/>
+      <c r="E17" s="4" t="inlineStr">
+        <is>
+          <t>Remote - India</t>
+        </is>
+      </c>
       <c r="F17" s="4" t="inlineStr">
         <is>
           <t>2026-09-07</t>
@@ -1219,12 +1223,12 @@
       </c>
       <c r="G17" s="5" t="inlineStr">
         <is>
-          <t>https://www.atlassian.com/company/careers/engineering/ai</t>
+          <t>https://databricks.com/company/careers/open-positions/job?gh_jid=8099751002</t>
         </is>
       </c>
       <c r="H17" s="4" t="inlineStr">
         <is>
-          <t>https://www.atlassian.com/company/careers/all-jobs</t>
+          <t>https://boards.greenhouse.io/databricks</t>
         </is>
       </c>
       <c r="I17" s="4" t="inlineStr">
@@ -1236,17 +1240,17 @@
     <row r="18">
       <c r="A18" s="4" t="inlineStr">
         <is>
-          <t>Databricks India</t>
+          <t>Exotel</t>
         </is>
       </c>
       <c r="B18" s="4" t="inlineStr">
         <is>
-          <t>AI Engineer - FDE (Forward Deployed Engineer)</t>
+          <t>Implementation Engineer 2</t>
         </is>
       </c>
       <c r="C18" s="4" t="inlineStr">
         <is>
-          <t>AI / ML</t>
+          <t>Software (General)</t>
         </is>
       </c>
       <c r="D18" s="4" t="inlineStr">
@@ -1256,7 +1260,7 @@
       </c>
       <c r="E18" s="4" t="inlineStr">
         <is>
-          <t>Remote - India</t>
+          <t>Bengaluru</t>
         </is>
       </c>
       <c r="F18" s="4" t="inlineStr">
@@ -1266,12 +1270,12 @@
       </c>
       <c r="G18" s="5" t="inlineStr">
         <is>
-          <t>https://databricks.com/company/careers/open-positions/job?gh_jid=8099751002</t>
+          <t>https://exotel.com/about-us/careers/#op-705944-implementation-engineer-2</t>
         </is>
       </c>
       <c r="H18" s="4" t="inlineStr">
         <is>
-          <t>https://boards.greenhouse.io/databricks</t>
+          <t>https://exotel.com/careers/</t>
         </is>
       </c>
       <c r="I18" s="4" t="inlineStr">
@@ -1288,12 +1292,12 @@
       </c>
       <c r="B19" s="4" t="inlineStr">
         <is>
-          <t>Implementation Engineer 2</t>
+          <t>Integration &amp; Customisation Engineer - 1 (PHP + React.JS)</t>
         </is>
       </c>
       <c r="C19" s="4" t="inlineStr">
         <is>
-          <t>Software (General)</t>
+          <t>Frontend</t>
         </is>
       </c>
       <c r="D19" s="4" t="inlineStr">
@@ -1303,7 +1307,7 @@
       </c>
       <c r="E19" s="4" t="inlineStr">
         <is>
-          <t>Bengaluru</t>
+          <t>India Full-time</t>
         </is>
       </c>
       <c r="F19" s="4" t="inlineStr">
@@ -1313,7 +1317,7 @@
       </c>
       <c r="G19" s="5" t="inlineStr">
         <is>
-          <t>https://exotel.com/about-us/careers/#op-705944-implementation-engineer-2</t>
+          <t>https://exotel.com/about-us/careers/#op-703033-integration--customisation-engineer-1-php--reactjs</t>
         </is>
       </c>
       <c r="H19" s="4" t="inlineStr">
@@ -1335,12 +1339,12 @@
       </c>
       <c r="B20" s="4" t="inlineStr">
         <is>
-          <t>Integration &amp; Customisation Engineer - 1 (PHP + React.JS)</t>
+          <t>Integration &amp; Customisation Engineer 2</t>
         </is>
       </c>
       <c r="C20" s="4" t="inlineStr">
         <is>
-          <t>Frontend</t>
+          <t>Software (General)</t>
         </is>
       </c>
       <c r="D20" s="4" t="inlineStr">
@@ -1360,7 +1364,7 @@
       </c>
       <c r="G20" s="5" t="inlineStr">
         <is>
-          <t>https://exotel.com/about-us/careers/#op-703033-integration--customisation-engineer-1-php--reactjs</t>
+          <t>https://exotel.com/about-us/careers/#op-694423-integration--customisation-engineer-2</t>
         </is>
       </c>
       <c r="H20" s="4" t="inlineStr">
@@ -1382,7 +1386,7 @@
       </c>
       <c r="B21" s="4" t="inlineStr">
         <is>
-          <t>Integration &amp; Customisation Engineer 2</t>
+          <t>Integration &amp; Customisation Engineer-1 (Chatbot)</t>
         </is>
       </c>
       <c r="C21" s="4" t="inlineStr">
@@ -1397,7 +1401,7 @@
       </c>
       <c r="E21" s="4" t="inlineStr">
         <is>
-          <t>India Full-time</t>
+          <t>Bengaluru/Gurugram Full-time</t>
         </is>
       </c>
       <c r="F21" s="4" t="inlineStr">
@@ -1407,7 +1411,7 @@
       </c>
       <c r="G21" s="5" t="inlineStr">
         <is>
-          <t>https://exotel.com/about-us/careers/#op-694423-integration--customisation-engineer-2</t>
+          <t>https://exotel.com/about-us/careers/#op-638792-integration--customisation-engineer1-chatbot</t>
         </is>
       </c>
       <c r="H21" s="4" t="inlineStr">
@@ -1429,7 +1433,7 @@
       </c>
       <c r="B22" s="4" t="inlineStr">
         <is>
-          <t>Integration &amp; Customisation Engineer-1 (Chatbot)</t>
+          <t>Integration &amp; Customization Engineer -1</t>
         </is>
       </c>
       <c r="C22" s="4" t="inlineStr">
@@ -1444,7 +1448,7 @@
       </c>
       <c r="E22" s="4" t="inlineStr">
         <is>
-          <t>Bengaluru/Gurugram Full-time</t>
+          <t>India Full-time</t>
         </is>
       </c>
       <c r="F22" s="4" t="inlineStr">
@@ -1454,7 +1458,7 @@
       </c>
       <c r="G22" s="5" t="inlineStr">
         <is>
-          <t>https://exotel.com/about-us/careers/#op-638792-integration--customisation-engineer1-chatbot</t>
+          <t>https://exotel.com/about-us/careers/#op-667737-integration--customization-engineer-1</t>
         </is>
       </c>
       <c r="H22" s="4" t="inlineStr">
@@ -1476,12 +1480,12 @@
       </c>
       <c r="B23" s="4" t="inlineStr">
         <is>
-          <t>Integration &amp; Customization Engineer -1</t>
+          <t>Product Support Intern</t>
         </is>
       </c>
       <c r="C23" s="4" t="inlineStr">
         <is>
-          <t>Software (General)</t>
+          <t>Intern</t>
         </is>
       </c>
       <c r="D23" s="4" t="inlineStr">
@@ -1491,7 +1495,7 @@
       </c>
       <c r="E23" s="4" t="inlineStr">
         <is>
-          <t>India Full-time</t>
+          <t>Bengaluru</t>
         </is>
       </c>
       <c r="F23" s="4" t="inlineStr">
@@ -1501,7 +1505,7 @@
       </c>
       <c r="G23" s="5" t="inlineStr">
         <is>
-          <t>https://exotel.com/about-us/careers/#op-667737-integration--customization-engineer-1</t>
+          <t>https://exotel.com/about-us/careers/#op-685404-product-support-intern-</t>
         </is>
       </c>
       <c r="H23" s="4" t="inlineStr">
@@ -1523,12 +1527,12 @@
       </c>
       <c r="B24" s="4" t="inlineStr">
         <is>
-          <t>Product Support Intern</t>
+          <t>Forward Deployed Engineer - 2</t>
         </is>
       </c>
       <c r="C24" s="4" t="inlineStr">
         <is>
-          <t>Intern</t>
+          <t>Software (General)</t>
         </is>
       </c>
       <c r="D24" s="4" t="inlineStr">
@@ -1548,7 +1552,7 @@
       </c>
       <c r="G24" s="5" t="inlineStr">
         <is>
-          <t>https://exotel.com/about-us/careers/#op-685404-product-support-intern-</t>
+          <t>https://exotel.com/about-us/careers/#op-705993-forward-deployed-engineer-2</t>
         </is>
       </c>
       <c r="H24" s="4" t="inlineStr">
@@ -1570,7 +1574,7 @@
       </c>
       <c r="B25" s="4" t="inlineStr">
         <is>
-          <t>Forward Deployed Engineer - 2</t>
+          <t>Product Head, Voice AI</t>
         </is>
       </c>
       <c r="C25" s="4" t="inlineStr">
@@ -1595,7 +1599,7 @@
       </c>
       <c r="G25" s="5" t="inlineStr">
         <is>
-          <t>https://exotel.com/about-us/careers/#op-705993-forward-deployed-engineer-2</t>
+          <t>https://exotel.com/about-us/careers/#op-705157-product-head-voice-ai</t>
         </is>
       </c>
       <c r="H25" s="4" t="inlineStr">
@@ -1617,12 +1621,12 @@
       </c>
       <c r="B26" s="4" t="inlineStr">
         <is>
-          <t>Product Head, Voice AI</t>
+          <t>Software Developer - 3 (Golang/Java/Python)</t>
         </is>
       </c>
       <c r="C26" s="4" t="inlineStr">
         <is>
-          <t>Software (General)</t>
+          <t>Backend</t>
         </is>
       </c>
       <c r="D26" s="4" t="inlineStr">
@@ -1642,7 +1646,7 @@
       </c>
       <c r="G26" s="5" t="inlineStr">
         <is>
-          <t>https://exotel.com/about-us/careers/#op-705157-product-head-voice-ai</t>
+          <t>https://exotel.com/about-us/careers/#op-701453-software-developer-3-golangjavapython</t>
         </is>
       </c>
       <c r="H26" s="4" t="inlineStr">
@@ -1664,12 +1668,12 @@
       </c>
       <c r="B27" s="4" t="inlineStr">
         <is>
-          <t>Software Developer - 3 (Golang/Java/Python)</t>
+          <t>Software Engineer - 2 (Voicebot)</t>
         </is>
       </c>
       <c r="C27" s="4" t="inlineStr">
         <is>
-          <t>Backend</t>
+          <t>Software (General)</t>
         </is>
       </c>
       <c r="D27" s="4" t="inlineStr">
@@ -1689,7 +1693,7 @@
       </c>
       <c r="G27" s="5" t="inlineStr">
         <is>
-          <t>https://exotel.com/about-us/careers/#op-701453-software-developer-3-golangjavapython</t>
+          <t>https://exotel.com/about-us/careers/#op-704060-software-engineer-2-voicebot</t>
         </is>
       </c>
       <c r="H27" s="4" t="inlineStr">
@@ -1706,17 +1710,17 @@
     <row r="28">
       <c r="A28" s="4" t="inlineStr">
         <is>
-          <t>Exotel</t>
+          <t>Fi Money</t>
         </is>
       </c>
       <c r="B28" s="4" t="inlineStr">
         <is>
-          <t>Software Engineer - 2 (Voicebot)</t>
+          <t>Ai Engg Intern</t>
         </is>
       </c>
       <c r="C28" s="4" t="inlineStr">
         <is>
-          <t>Software (General)</t>
+          <t>Intern</t>
         </is>
       </c>
       <c r="D28" s="4" t="inlineStr">
@@ -1726,7 +1730,7 @@
       </c>
       <c r="E28" s="4" t="inlineStr">
         <is>
-          <t>Bengaluru</t>
+          <t>Bangalore</t>
         </is>
       </c>
       <c r="F28" s="4" t="inlineStr">
@@ -1736,12 +1740,12 @@
       </c>
       <c r="G28" s="5" t="inlineStr">
         <is>
-          <t>https://exotel.com/about-us/careers/#op-704060-software-engineer-2-voicebot</t>
+          <t>https://jobs.lever.co/epifi/08c743e8-2b29-4f78-827e-5bd90476ed86</t>
         </is>
       </c>
       <c r="H28" s="4" t="inlineStr">
         <is>
-          <t>https://exotel.com/careers/</t>
+          <t>https://jobs.lever.co/epifi</t>
         </is>
       </c>
       <c r="I28" s="4" t="inlineStr">
@@ -1758,7 +1762,7 @@
       </c>
       <c r="B29" s="4" t="inlineStr">
         <is>
-          <t>Ai Engg Intern</t>
+          <t>DS/ML Intern</t>
         </is>
       </c>
       <c r="C29" s="4" t="inlineStr">
@@ -1783,7 +1787,7 @@
       </c>
       <c r="G29" s="5" t="inlineStr">
         <is>
-          <t>https://jobs.lever.co/epifi/08c743e8-2b29-4f78-827e-5bd90476ed86</t>
+          <t>https://jobs.lever.co/epifi/08fc1577-4593-4b94-b66b-08e638d29f37</t>
         </is>
       </c>
       <c r="H29" s="4" t="inlineStr">
@@ -1805,7 +1809,7 @@
       </c>
       <c r="B30" s="4" t="inlineStr">
         <is>
-          <t>DS/ML Intern</t>
+          <t>GenAI Product Builder Intern</t>
         </is>
       </c>
       <c r="C30" s="4" t="inlineStr">
@@ -1830,7 +1834,7 @@
       </c>
       <c r="G30" s="5" t="inlineStr">
         <is>
-          <t>https://jobs.lever.co/epifi/08fc1577-4593-4b94-b66b-08e638d29f37</t>
+          <t>https://jobs.lever.co/epifi/4f5b7548-ea0a-4be0-816b-11d712853169</t>
         </is>
       </c>
       <c r="H30" s="4" t="inlineStr">
@@ -1847,17 +1851,17 @@
     <row r="31">
       <c r="A31" s="4" t="inlineStr">
         <is>
-          <t>Fi Money</t>
+          <t>Fractal Analytics</t>
         </is>
       </c>
       <c r="B31" s="4" t="inlineStr">
         <is>
-          <t>GenAI Product Builder Intern</t>
+          <t>Python Backend Engineer</t>
         </is>
       </c>
       <c r="C31" s="4" t="inlineStr">
         <is>
-          <t>Intern</t>
+          <t>Backend</t>
         </is>
       </c>
       <c r="D31" s="4" t="inlineStr">
@@ -1865,11 +1869,7 @@
           <t>Not specified</t>
         </is>
       </c>
-      <c r="E31" s="4" t="inlineStr">
-        <is>
-          <t>Bangalore</t>
-        </is>
-      </c>
+      <c r="E31" s="4" t="inlineStr"/>
       <c r="F31" s="4" t="inlineStr">
         <is>
           <t>2026-09-07</t>
@@ -1877,12 +1877,12 @@
       </c>
       <c r="G31" s="5" t="inlineStr">
         <is>
-          <t>https://jobs.lever.co/epifi/4f5b7548-ea0a-4be0-816b-11d712853169</t>
+          <t>https://fractal.ai/en-US/Careers/job/Texas/Data-Engineer-Business-Intelligence-Senior-Consultant-Architect-6_SR-43710-1</t>
         </is>
       </c>
       <c r="H31" s="4" t="inlineStr">
         <is>
-          <t>https://jobs.lever.co/epifi</t>
+          <t>https://fractal.ai/careers/</t>
         </is>
       </c>
       <c r="I31" s="4" t="inlineStr">
@@ -1899,12 +1899,12 @@
       </c>
       <c r="B32" s="4" t="inlineStr">
         <is>
-          <t>Python Backend Engineer</t>
+          <t>AI Engineer</t>
         </is>
       </c>
       <c r="C32" s="4" t="inlineStr">
         <is>
-          <t>Backend</t>
+          <t>AI / ML</t>
         </is>
       </c>
       <c r="D32" s="4" t="inlineStr">
@@ -1920,7 +1920,7 @@
       </c>
       <c r="G32" s="5" t="inlineStr">
         <is>
-          <t>https://fractal.ai/en-US/Careers/job/Texas/Data-Engineer-Business-Intelligence-Senior-Consultant-Architect-6_SR-43710-1</t>
+          <t>https://fractal.ai/en-US/Careers/job/Texas/AI-Engineer_SR-45356-1</t>
         </is>
       </c>
       <c r="H32" s="4" t="inlineStr">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="B33" s="4" t="inlineStr">
         <is>
-          <t>AI Engineer</t>
+          <t>SharePoint Full Stack role</t>
         </is>
       </c>
       <c r="C33" s="4" t="inlineStr">
         <is>
-          <t>AI / ML</t>
+          <t>Full Stack</t>
         </is>
       </c>
       <c r="D33" s="4" t="inlineStr">
@@ -1963,7 +1963,7 @@
       </c>
       <c r="G33" s="5" t="inlineStr">
         <is>
-          <t>https://fractal.ai/en-US/Careers/job/Texas/AI-Engineer_SR-45356-1</t>
+          <t>https://fractal.ai/en-US/Careers/job/Texas/SharePoint-Full-Stack-role_SR-42495-1</t>
         </is>
       </c>
       <c r="H33" s="4" t="inlineStr">
@@ -1980,17 +1980,17 @@
     <row r="34">
       <c r="A34" s="4" t="inlineStr">
         <is>
-          <t>Fractal Analytics</t>
+          <t>Freshworks</t>
         </is>
       </c>
       <c r="B34" s="4" t="inlineStr">
         <is>
-          <t>SharePoint Full Stack role</t>
+          <t>Specialist - Data Platform Engineering</t>
         </is>
       </c>
       <c r="C34" s="4" t="inlineStr">
         <is>
-          <t>Full Stack</t>
+          <t>DevOps / SRE</t>
         </is>
       </c>
       <c r="D34" s="4" t="inlineStr">
@@ -1998,7 +1998,11 @@
           <t>Not specified</t>
         </is>
       </c>
-      <c r="E34" s="4" t="inlineStr"/>
+      <c r="E34" s="4" t="inlineStr">
+        <is>
+          <t>Chennai, in</t>
+        </is>
+      </c>
       <c r="F34" s="4" t="inlineStr">
         <is>
           <t>2026-09-07</t>
@@ -2006,12 +2010,12 @@
       </c>
       <c r="G34" s="5" t="inlineStr">
         <is>
-          <t>https://fractal.ai/en-US/Careers/job/Texas/SharePoint-Full-Stack-role_SR-42495-1</t>
+          <t>https://api.smartrecruiters.com/v1/companies/Freshworks/postings/744000143102264</t>
         </is>
       </c>
       <c r="H34" s="4" t="inlineStr">
         <is>
-          <t>https://fractal.ai/careers/</t>
+          <t>https://careers.smartrecruiters.com/Freshworks</t>
         </is>
       </c>
       <c r="I34" s="4" t="inlineStr">
@@ -2023,17 +2027,17 @@
     <row r="35">
       <c r="A35" s="4" t="inlineStr">
         <is>
-          <t>Freshworks</t>
+          <t>GitLab India</t>
         </is>
       </c>
       <c r="B35" s="4" t="inlineStr">
         <is>
-          <t>Specialist - Data Platform Engineering</t>
+          <t>Software composition analysis</t>
         </is>
       </c>
       <c r="C35" s="4" t="inlineStr">
         <is>
-          <t>DevOps / SRE</t>
+          <t>Software (General)</t>
         </is>
       </c>
       <c r="D35" s="4" t="inlineStr">
@@ -2041,11 +2045,7 @@
           <t>Not specified</t>
         </is>
       </c>
-      <c r="E35" s="4" t="inlineStr">
-        <is>
-          <t>Chennai, in</t>
-        </is>
-      </c>
+      <c r="E35" s="4" t="inlineStr"/>
       <c r="F35" s="4" t="inlineStr">
         <is>
           <t>2026-09-07</t>
@@ -2053,12 +2053,12 @@
       </c>
       <c r="G35" s="5" t="inlineStr">
         <is>
-          <t>https://api.smartrecruiters.com/v1/companies/Freshworks/postings/744000143102264</t>
+          <t>https://about.gitlab.com/solutions/supply-chain/</t>
         </is>
       </c>
       <c r="H35" s="4" t="inlineStr">
         <is>
-          <t>https://careers.smartrecruiters.com/Freshworks</t>
+          <t>https://about.gitlab.com/jobs/all-jobs/</t>
         </is>
       </c>
       <c r="I35" s="4" t="inlineStr">
@@ -2070,17 +2070,17 @@
     <row r="36">
       <c r="A36" s="4" t="inlineStr">
         <is>
-          <t>GitLab India</t>
+          <t>Goldman Sachs India</t>
         </is>
       </c>
       <c r="B36" s="4" t="inlineStr">
         <is>
-          <t>Software composition analysis</t>
+          <t>Internships and Programs</t>
         </is>
       </c>
       <c r="C36" s="4" t="inlineStr">
         <is>
-          <t>Software (General)</t>
+          <t>Intern</t>
         </is>
       </c>
       <c r="D36" s="4" t="inlineStr">
@@ -2096,12 +2096,12 @@
       </c>
       <c r="G36" s="5" t="inlineStr">
         <is>
-          <t>https://about.gitlab.com/solutions/supply-chain/</t>
+          <t>https://www.goldmansachs.com/careers/students/programs-and-internships</t>
         </is>
       </c>
       <c r="H36" s="4" t="inlineStr">
         <is>
-          <t>https://about.gitlab.com/jobs/all-jobs/</t>
+          <t>https://www.goldmansachs.com/careers/</t>
         </is>
       </c>
       <c r="I36" s="4" t="inlineStr">
@@ -2118,12 +2118,12 @@
       </c>
       <c r="B37" s="4" t="inlineStr">
         <is>
-          <t>Internships and Programs</t>
+          <t>Engineering Envisions, builds, and deploys industry-leading innovations that drive our business and extend boundaries.</t>
         </is>
       </c>
       <c r="C37" s="4" t="inlineStr">
         <is>
-          <t>Intern</t>
+          <t>Software (General)</t>
         </is>
       </c>
       <c r="D37" s="4" t="inlineStr">
@@ -2139,7 +2139,7 @@
       </c>
       <c r="G37" s="5" t="inlineStr">
         <is>
-          <t>https://www.goldmansachs.com/careers/students/programs-and-internships</t>
+          <t>https://www.goldmansachs.com/careers/our-firm/engineering</t>
         </is>
       </c>
       <c r="H37" s="4" t="inlineStr">
@@ -2156,17 +2156,17 @@
     <row r="38">
       <c r="A38" s="4" t="inlineStr">
         <is>
-          <t>Goldman Sachs India</t>
+          <t>Groww</t>
         </is>
       </c>
       <c r="B38" s="4" t="inlineStr">
         <is>
-          <t>Engineering Envisions, builds, and deploys industry-leading innovations that drive our business and extend boundaries.</t>
+          <t>Video Editor Intern</t>
         </is>
       </c>
       <c r="C38" s="4" t="inlineStr">
         <is>
-          <t>Software (General)</t>
+          <t>Intern</t>
         </is>
       </c>
       <c r="D38" s="4" t="inlineStr">
@@ -2174,7 +2174,11 @@
           <t>Not specified</t>
         </is>
       </c>
-      <c r="E38" s="4" t="inlineStr"/>
+      <c r="E38" s="4" t="inlineStr">
+        <is>
+          <t>Bengaluru-VTP, India</t>
+        </is>
+      </c>
       <c r="F38" s="4" t="inlineStr">
         <is>
           <t>2026-09-07</t>
@@ -2182,12 +2186,12 @@
       </c>
       <c r="G38" s="5" t="inlineStr">
         <is>
-          <t>https://www.goldmansachs.com/careers/our-firm/engineering</t>
+          <t>https://job-boards.eu.greenhouse.io/groww/jobs/4956817101</t>
         </is>
       </c>
       <c r="H38" s="4" t="inlineStr">
         <is>
-          <t>https://www.goldmansachs.com/careers/</t>
+          <t>https://boards.greenhouse.io/groww</t>
         </is>
       </c>
       <c r="I38" s="4" t="inlineStr">
@@ -2204,7 +2208,7 @@
       </c>
       <c r="B39" s="4" t="inlineStr">
         <is>
-          <t>Video Editor Intern</t>
+          <t>YouTube &amp; Content - Internship</t>
         </is>
       </c>
       <c r="C39" s="4" t="inlineStr">
@@ -2229,7 +2233,7 @@
       </c>
       <c r="G39" s="5" t="inlineStr">
         <is>
-          <t>https://job-boards.eu.greenhouse.io/groww/jobs/4956817101</t>
+          <t>https://job-boards.eu.greenhouse.io/groww/jobs/4967486101</t>
         </is>
       </c>
       <c r="H39" s="4" t="inlineStr">
@@ -2246,17 +2250,17 @@
     <row r="40">
       <c r="A40" s="4" t="inlineStr">
         <is>
-          <t>Groww</t>
+          <t>HighRadius</t>
         </is>
       </c>
       <c r="B40" s="4" t="inlineStr">
         <is>
-          <t>YouTube &amp; Content - Internship</t>
+          <t>Cloud Security Engineer</t>
         </is>
       </c>
       <c r="C40" s="4" t="inlineStr">
         <is>
-          <t>Intern</t>
+          <t>Software (General)</t>
         </is>
       </c>
       <c r="D40" s="4" t="inlineStr">
@@ -2266,7 +2270,7 @@
       </c>
       <c r="E40" s="4" t="inlineStr">
         <is>
-          <t>Bengaluru-VTP, India</t>
+          <t>Hyderabad, Telangana, India</t>
         </is>
       </c>
       <c r="F40" s="4" t="inlineStr">
@@ -2276,12 +2280,12 @@
       </c>
       <c r="G40" s="5" t="inlineStr">
         <is>
-          <t>https://job-boards.eu.greenhouse.io/groww/jobs/4967486101</t>
+          <t>https://www.highradius.com/about/careers-list/?gh_jid=7511618003</t>
         </is>
       </c>
       <c r="H40" s="4" t="inlineStr">
         <is>
-          <t>https://boards.greenhouse.io/groww</t>
+          <t>https://boards.greenhouse.io/highradius</t>
         </is>
       </c>
       <c r="I40" s="4" t="inlineStr">
@@ -2293,12 +2297,12 @@
     <row r="41">
       <c r="A41" s="4" t="inlineStr">
         <is>
-          <t>HighRadius</t>
+          <t>Ixigo</t>
         </is>
       </c>
       <c r="B41" s="4" t="inlineStr">
         <is>
-          <t>Cloud Security Engineer</t>
+          <t>Research Engineer - Agent Intelligence &amp; Evaluation</t>
         </is>
       </c>
       <c r="C41" s="4" t="inlineStr">
@@ -2313,7 +2317,7 @@
       </c>
       <c r="E41" s="4" t="inlineStr">
         <is>
-          <t>Hyderabad, Telangana, India</t>
+          <t>New Delhi, in</t>
         </is>
       </c>
       <c r="F41" s="4" t="inlineStr">
@@ -2323,12 +2327,12 @@
       </c>
       <c r="G41" s="5" t="inlineStr">
         <is>
-          <t>https://www.highradius.com/about/careers-list/?gh_jid=7511618003</t>
+          <t>https://api.smartrecruiters.com/v1/companies/ixigo/postings/744000144034719</t>
         </is>
       </c>
       <c r="H41" s="4" t="inlineStr">
         <is>
-          <t>https://boards.greenhouse.io/highradius</t>
+          <t>https://careers.smartrecruiters.com/ixigo</t>
         </is>
       </c>
       <c r="I41" s="4" t="inlineStr">
@@ -2345,12 +2349,12 @@
       </c>
       <c r="B42" s="4" t="inlineStr">
         <is>
-          <t>Research Engineer - Agent Intelligence &amp; Evaluation</t>
+          <t>Machine Learning Engineer (Agent Intelligence &amp; Evaluations)</t>
         </is>
       </c>
       <c r="C42" s="4" t="inlineStr">
         <is>
-          <t>Software (General)</t>
+          <t>AI / ML</t>
         </is>
       </c>
       <c r="D42" s="4" t="inlineStr">
@@ -2370,7 +2374,7 @@
       </c>
       <c r="G42" s="5" t="inlineStr">
         <is>
-          <t>https://api.smartrecruiters.com/v1/companies/ixigo/postings/744000144034719</t>
+          <t>https://api.smartrecruiters.com/v1/companies/ixigo/postings/744000143976319</t>
         </is>
       </c>
       <c r="H42" s="4" t="inlineStr">
@@ -2392,12 +2396,12 @@
       </c>
       <c r="B43" s="4" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer (Agent Intelligence &amp; Evaluations)</t>
+          <t xml:space="preserve"> Software Engineer - 2 Backend</t>
         </is>
       </c>
       <c r="C43" s="4" t="inlineStr">
         <is>
-          <t>AI / ML</t>
+          <t>Backend</t>
         </is>
       </c>
       <c r="D43" s="4" t="inlineStr">
@@ -2407,7 +2411,7 @@
       </c>
       <c r="E43" s="4" t="inlineStr">
         <is>
-          <t>New Delhi, in</t>
+          <t>Gurugram, in</t>
         </is>
       </c>
       <c r="F43" s="4" t="inlineStr">
@@ -2417,7 +2421,7 @@
       </c>
       <c r="G43" s="5" t="inlineStr">
         <is>
-          <t>https://api.smartrecruiters.com/v1/companies/ixigo/postings/744000143976319</t>
+          <t>https://api.smartrecruiters.com/v1/companies/ixigo/postings/744000143738909</t>
         </is>
       </c>
       <c r="H43" s="4" t="inlineStr">
@@ -2434,12 +2438,12 @@
     <row r="44">
       <c r="A44" s="4" t="inlineStr">
         <is>
-          <t>Ixigo</t>
+          <t>Lendingkart</t>
         </is>
       </c>
       <c r="B44" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Software Engineer - 2 Backend</t>
+          <t>Backend Developer</t>
         </is>
       </c>
       <c r="C44" s="4" t="inlineStr">
@@ -2454,7 +2458,7 @@
       </c>
       <c r="E44" s="4" t="inlineStr">
         <is>
-          <t>Gurugram, in</t>
+          <t>Bengaluru, in</t>
         </is>
       </c>
       <c r="F44" s="4" t="inlineStr">
@@ -2464,12 +2468,12 @@
       </c>
       <c r="G44" s="5" t="inlineStr">
         <is>
-          <t>https://api.smartrecruiters.com/v1/companies/ixigo/postings/744000143738909</t>
+          <t>https://api.smartrecruiters.com/v1/companies/lendingkart/postings/82097348</t>
         </is>
       </c>
       <c r="H44" s="4" t="inlineStr">
         <is>
-          <t>https://careers.smartrecruiters.com/ixigo</t>
+          <t>https://careers.smartrecruiters.com/lendingkart</t>
         </is>
       </c>
       <c r="I44" s="4" t="inlineStr">
@@ -2481,17 +2485,17 @@
     <row r="45">
       <c r="A45" s="4" t="inlineStr">
         <is>
-          <t>Lendingkart</t>
+          <t>Licious</t>
         </is>
       </c>
       <c r="B45" s="4" t="inlineStr">
         <is>
-          <t>Backend Developer</t>
+          <t>By: Licious DevOps</t>
         </is>
       </c>
       <c r="C45" s="4" t="inlineStr">
         <is>
-          <t>Backend</t>
+          <t>DevOps / SRE</t>
         </is>
       </c>
       <c r="D45" s="4" t="inlineStr">
@@ -2499,11 +2503,7 @@
           <t>Not specified</t>
         </is>
       </c>
-      <c r="E45" s="4" t="inlineStr">
-        <is>
-          <t>Bengaluru, in</t>
-        </is>
-      </c>
+      <c r="E45" s="4" t="inlineStr"/>
       <c r="F45" s="4" t="inlineStr">
         <is>
           <t>2026-09-07</t>
@@ -2511,12 +2511,12 @@
       </c>
       <c r="G45" s="5" t="inlineStr">
         <is>
-          <t>https://api.smartrecruiters.com/v1/companies/lendingkart/postings/82097348</t>
+          <t>https://careers.licious.com/author/adminlic/</t>
         </is>
       </c>
       <c r="H45" s="4" t="inlineStr">
         <is>
-          <t>https://careers.smartrecruiters.com/lendingkart</t>
+          <t>https://www.licious.in/careers</t>
         </is>
       </c>
       <c r="I45" s="4" t="inlineStr">
@@ -2528,17 +2528,17 @@
     <row r="46">
       <c r="A46" s="4" t="inlineStr">
         <is>
-          <t>Licious</t>
+          <t>LinkedIn India</t>
         </is>
       </c>
       <c r="B46" s="4" t="inlineStr">
         <is>
-          <t>By: Licious DevOps</t>
+          <t>Internship Opportunities</t>
         </is>
       </c>
       <c r="C46" s="4" t="inlineStr">
         <is>
-          <t>DevOps / SRE</t>
+          <t>Intern</t>
         </is>
       </c>
       <c r="D46" s="4" t="inlineStr">
@@ -2554,12 +2554,12 @@
       </c>
       <c r="G46" s="5" t="inlineStr">
         <is>
-          <t>https://careers.licious.com/author/adminlic/</t>
+          <t>https://careers.linkedin.com/pathways-programs/internships</t>
         </is>
       </c>
       <c r="H46" s="4" t="inlineStr">
         <is>
-          <t>https://www.licious.in/careers</t>
+          <t>https://careers.linkedin.com/</t>
         </is>
       </c>
       <c r="I46" s="4" t="inlineStr">
@@ -2576,12 +2576,12 @@
       </c>
       <c r="B47" s="4" t="inlineStr">
         <is>
-          <t>Internship Opportunities</t>
+          <t>Engineering</t>
         </is>
       </c>
       <c r="C47" s="4" t="inlineStr">
         <is>
-          <t>Intern</t>
+          <t>Software (General)</t>
         </is>
       </c>
       <c r="D47" s="4" t="inlineStr">
@@ -2597,7 +2597,7 @@
       </c>
       <c r="G47" s="5" t="inlineStr">
         <is>
-          <t>https://careers.linkedin.com/pathways-programs/internships</t>
+          <t>https://careers.linkedin.com/Teams/Engineering</t>
         </is>
       </c>
       <c r="H47" s="4" t="inlineStr">
@@ -2614,12 +2614,12 @@
     <row r="48">
       <c r="A48" s="4" t="inlineStr">
         <is>
-          <t>LinkedIn India</t>
+          <t>MoEngage</t>
         </is>
       </c>
       <c r="B48" s="4" t="inlineStr">
         <is>
-          <t>Engineering</t>
+          <t>For Developers</t>
         </is>
       </c>
       <c r="C48" s="4" t="inlineStr">
@@ -2640,12 +2640,12 @@
       </c>
       <c r="G48" s="5" t="inlineStr">
         <is>
-          <t>https://careers.linkedin.com/Teams/Engineering</t>
+          <t>https://www.moengage.com/role/for-developers/</t>
         </is>
       </c>
       <c r="H48" s="4" t="inlineStr">
         <is>
-          <t>https://careers.linkedin.com/</t>
+          <t>https://www.moengage.com/careers/</t>
         </is>
       </c>
       <c r="I48" s="4" t="inlineStr">
@@ -2657,12 +2657,12 @@
     <row r="49">
       <c r="A49" s="4" t="inlineStr">
         <is>
-          <t>MoEngage</t>
+          <t>MongoDB India</t>
         </is>
       </c>
       <c r="B49" s="4" t="inlineStr">
         <is>
-          <t>For Developers</t>
+          <t>Software Engineer 3</t>
         </is>
       </c>
       <c r="C49" s="4" t="inlineStr">
@@ -2675,7 +2675,11 @@
           <t>Not specified</t>
         </is>
       </c>
-      <c r="E49" s="4" t="inlineStr"/>
+      <c r="E49" s="4" t="inlineStr">
+        <is>
+          <t>Gurugram</t>
+        </is>
+      </c>
       <c r="F49" s="4" t="inlineStr">
         <is>
           <t>2026-09-07</t>
@@ -2683,12 +2687,12 @@
       </c>
       <c r="G49" s="5" t="inlineStr">
         <is>
-          <t>https://www.moengage.com/role/for-developers/</t>
+          <t>https://www.mongodb.com/careers/job/?gh_jid=8167389</t>
         </is>
       </c>
       <c r="H49" s="4" t="inlineStr">
         <is>
-          <t>https://www.moengage.com/careers/</t>
+          <t>https://boards.greenhouse.io/mongodb</t>
         </is>
       </c>
       <c r="I49" s="4" t="inlineStr">
@@ -2700,17 +2704,17 @@
     <row r="50">
       <c r="A50" s="4" t="inlineStr">
         <is>
-          <t>MongoDB India</t>
+          <t>Mphasis</t>
         </is>
       </c>
       <c r="B50" s="4" t="inlineStr">
         <is>
-          <t>Software Engineer 3</t>
+          <t>TESTING</t>
         </is>
       </c>
       <c r="C50" s="4" t="inlineStr">
         <is>
-          <t>Software (General)</t>
+          <t>QA / SDET</t>
         </is>
       </c>
       <c r="D50" s="4" t="inlineStr">
@@ -2718,11 +2722,7 @@
           <t>Not specified</t>
         </is>
       </c>
-      <c r="E50" s="4" t="inlineStr">
-        <is>
-          <t>Gurugram</t>
-        </is>
-      </c>
+      <c r="E50" s="4" t="inlineStr"/>
       <c r="F50" s="4" t="inlineStr">
         <is>
           <t>2026-09-07</t>
@@ -2730,12 +2730,12 @@
       </c>
       <c r="G50" s="5" t="inlineStr">
         <is>
-          <t>https://www.mongodb.com/careers/job/?gh_jid=8167389</t>
+          <t>https://careers.mphasis.com/home/hot-jobs/skill-search/testing-jobs.html</t>
         </is>
       </c>
       <c r="H50" s="4" t="inlineStr">
         <is>
-          <t>https://boards.greenhouse.io/mongodb</t>
+          <t>https://careers.mphasis.com/</t>
         </is>
       </c>
       <c r="I50" s="4" t="inlineStr">
@@ -2747,25 +2747,29 @@
     <row r="51">
       <c r="A51" s="4" t="inlineStr">
         <is>
-          <t>Mphasis</t>
+          <t>Okta India</t>
         </is>
       </c>
       <c r="B51" s="4" t="inlineStr">
         <is>
-          <t>TESTING</t>
+          <t>SRE Operations Engineer</t>
         </is>
       </c>
       <c r="C51" s="4" t="inlineStr">
         <is>
-          <t>QA / SDET</t>
+          <t>DevOps / SRE</t>
         </is>
       </c>
       <c r="D51" s="4" t="inlineStr">
         <is>
-          <t>Not specified</t>
-        </is>
-      </c>
-      <c r="E51" s="4" t="inlineStr"/>
+          <t>1+ years</t>
+        </is>
+      </c>
+      <c r="E51" s="4" t="inlineStr">
+        <is>
+          <t>Bengaluru, India</t>
+        </is>
+      </c>
       <c r="F51" s="4" t="inlineStr">
         <is>
           <t>2026-09-07</t>
@@ -2773,12 +2777,12 @@
       </c>
       <c r="G51" s="5" t="inlineStr">
         <is>
-          <t>https://careers.mphasis.com/home/hot-jobs/skill-search/testing-jobs.html</t>
+          <t>https://www.okta.com/company/careers/opportunity/8003315?gh_jid=8003315</t>
         </is>
       </c>
       <c r="H51" s="4" t="inlineStr">
         <is>
-          <t>https://careers.mphasis.com/</t>
+          <t>https://boards.greenhouse.io/okta</t>
         </is>
       </c>
       <c r="I51" s="4" t="inlineStr">
@@ -4032,8 +4036,55 @@
         </is>
       </c>
     </row>
+    <row r="79">
+      <c r="A79" s="4" t="inlineStr">
+        <is>
+          <t>Zscaler India</t>
+        </is>
+      </c>
+      <c r="B79" s="4" t="inlineStr">
+        <is>
+          <t>Software Development Engineer</t>
+        </is>
+      </c>
+      <c r="C79" s="4" t="inlineStr">
+        <is>
+          <t>Software (General)</t>
+        </is>
+      </c>
+      <c r="D79" s="4" t="inlineStr">
+        <is>
+          <t>1 - 3 years</t>
+        </is>
+      </c>
+      <c r="E79" s="4" t="inlineStr">
+        <is>
+          <t>Bangalore, IND</t>
+        </is>
+      </c>
+      <c r="F79" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="G79" s="5" t="inlineStr">
+        <is>
+          <t>https://job-boards.greenhouse.io/zscaler/jobs/5219488007</t>
+        </is>
+      </c>
+      <c r="H79" s="4" t="inlineStr">
+        <is>
+          <t>https://boards.greenhouse.io/zscaler</t>
+        </is>
+      </c>
+      <c r="I79" s="4" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:I78"/>
+  <autoFilter ref="A1:I79"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G3" r:id="rId2"/>
@@ -4112,6 +4163,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G76" r:id="rId75"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G77" r:id="rId76"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G78" r:id="rId77"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G79" r:id="rId78"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -4123,7 +4175,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C16"/>
+  <dimension ref="A1:C24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -4191,15 +4243,35 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
+          <t>Plivo</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>https://www.plivo.com/careers/</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">playwright failed: Page.goto: Timeout 25000ms exceeded.
+Call log:
+  - navigating to "https://www.plivo.com/careers/", waiting until "networkidle"
+</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
           <t>Signzy</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
+      <c r="B5" t="inlineStr">
         <is>
           <t>https://www.signzy.com/careers/</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
+      <c r="C5" t="inlineStr">
         <is>
           <t xml:space="preserve">playwright failed: Page.goto: Timeout 25000ms exceeded.
 Call log:
@@ -4208,18 +4280,58 @@
         </is>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Vymo</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>https://getvymo.com/careers/</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">playwright failed: Page.goto: Timeout 25000ms exceeded.
+Call log:
+  - navigating to "https://getvymo.com/careers/", waiting until "networkidle"
+</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Zluri</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>https://www.zluri.com/careers</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">playwright failed: Page.goto: Timeout 25000ms exceeded.
+Call log:
+  - navigating to "https://www.zluri.com/careers", waiting until "networkidle"
+</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
         <is>
           <t>Ather Energy</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
+      <c r="B8" t="inlineStr">
         <is>
           <t>https://www.atherenergy.com/careers</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
+      <c r="C8" t="inlineStr">
         <is>
           <t xml:space="preserve">playwright failed: Page.goto: Timeout 25000ms exceeded.
 Call log:
@@ -4228,18 +4340,18 @@
         </is>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
+    <row r="9">
+      <c r="A9" t="inlineStr">
         <is>
           <t>Capillary Technologies</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
+      <c r="B9" t="inlineStr">
         <is>
           <t>https://www.capillarytech.com/careers/</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr">
+      <c r="C9" t="inlineStr">
         <is>
           <t xml:space="preserve">playwright failed: Page.goto: Timeout 25000ms exceeded.
 Call log:
@@ -4248,18 +4360,18 @@
         </is>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
+    <row r="10">
+      <c r="A10" t="inlineStr">
         <is>
           <t>Darwinbox</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
+      <c r="B10" t="inlineStr">
         <is>
           <t>https://darwinbox.com/careers</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr">
+      <c r="C10" t="inlineStr">
         <is>
           <t xml:space="preserve">playwright failed: Page.goto: Timeout 25000ms exceeded.
 Call log:
@@ -4268,18 +4380,18 @@
         </is>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
+    <row r="11">
+      <c r="A11" t="inlineStr">
         <is>
           <t>Nykaa</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
+      <c r="B11" t="inlineStr">
         <is>
           <t>https://www.nykaa.com/careers</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr">
+      <c r="C11" t="inlineStr">
         <is>
           <t xml:space="preserve">playwright failed: Page.goto: net::ERR_HTTP2_PROTOCOL_ERROR at https://www.nykaa.com/careers
 Call log:
@@ -4288,18 +4400,18 @@
         </is>
       </c>
     </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
+    <row r="12">
+      <c r="A12" t="inlineStr">
         <is>
           <t>Juspay</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
+      <c r="B12" t="inlineStr">
         <is>
           <t>https://juspay.io/careers</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr">
+      <c r="C12" t="inlineStr">
         <is>
           <t xml:space="preserve">playwright failed: Page.goto: Timeout 25000ms exceeded.
 Call log:
@@ -4308,18 +4420,38 @@
         </is>
       </c>
     </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>LatentView Analytics</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>https://www.latentview.com/careers/</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">playwright failed: Page.goto: Timeout 25000ms exceeded.
+Call log:
+  - navigating to "https://www.latentview.com/careers/", waiting until "networkidle"
+</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
         <is>
           <t>MakeMyTrip</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr">
+      <c r="B14" t="inlineStr">
         <is>
           <t>https://careers.makemytrip.com/</t>
         </is>
       </c>
-      <c r="C10" t="inlineStr">
+      <c r="C14" t="inlineStr">
         <is>
           <t xml:space="preserve">playwright failed: Page.goto: Timeout 25000ms exceeded.
 Call log:
@@ -4328,18 +4460,18 @@
         </is>
       </c>
     </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
+    <row r="15">
+      <c r="A15" t="inlineStr">
         <is>
           <t>FirstCry</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr">
+      <c r="B15" t="inlineStr">
         <is>
           <t>https://www.firstcry.com/careers</t>
         </is>
       </c>
-      <c r="C11" t="inlineStr">
+      <c r="C15" t="inlineStr">
         <is>
           <t xml:space="preserve">playwright failed: Page.goto: Timeout 25000ms exceeded.
 Call log:
@@ -4348,18 +4480,38 @@
         </is>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>OYO</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>https://www.oyorooms.com/careers/</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">playwright failed: Page.goto: Timeout 25000ms exceeded.
+Call log:
+  - navigating to "https://www.oyorooms.com/careers/", waiting until "networkidle"
+</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
         <is>
           <t>Zomato</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr">
+      <c r="B17" t="inlineStr">
         <is>
           <t>https://www.zomato.com/careers</t>
         </is>
       </c>
-      <c r="C12" t="inlineStr">
+      <c r="C17" t="inlineStr">
         <is>
           <t xml:space="preserve">playwright failed: Page.goto: net::ERR_HTTP2_PROTOCOL_ERROR at https://www.zomato.com/careers
 Call log:
@@ -4368,18 +4520,38 @@
         </is>
       </c>
     </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Rapido</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>https://rapido.bike/careers</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">playwright failed: Page.goto: Timeout 25000ms exceeded.
+Call log:
+  - navigating to "https://rapido.bike/careers", waiting until "networkidle"
+</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
         <is>
           <t>Coforge</t>
         </is>
       </c>
-      <c r="B13" t="inlineStr">
+      <c r="B19" t="inlineStr">
         <is>
           <t>https://www.coforge.com/careers</t>
         </is>
       </c>
-      <c r="C13" t="inlineStr">
+      <c r="C19" t="inlineStr">
         <is>
           <t xml:space="preserve">playwright failed: Page.goto: net::ERR_HTTP2_PROTOCOL_ERROR at https://www.coforge.com/careers
 Call log:
@@ -4388,18 +4560,18 @@
         </is>
       </c>
     </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
+    <row r="20">
+      <c r="A20" t="inlineStr">
         <is>
           <t>Persistent Systems</t>
         </is>
       </c>
-      <c r="B14" t="inlineStr">
+      <c r="B20" t="inlineStr">
         <is>
           <t>https://www.persistent.com/careers/</t>
         </is>
       </c>
-      <c r="C14" t="inlineStr">
+      <c r="C20" t="inlineStr">
         <is>
           <t xml:space="preserve">playwright failed: Page.goto: net::ERR_HTTP2_PROTOCOL_ERROR at https://www.persistent.com/careers/
 Call log:
@@ -4408,18 +4580,18 @@
         </is>
       </c>
     </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
+    <row r="21">
+      <c r="A21" t="inlineStr">
         <is>
           <t>upGrad</t>
         </is>
       </c>
-      <c r="B15" t="inlineStr">
+      <c r="B21" t="inlineStr">
         <is>
           <t>https://www.upgrad.com/careers/</t>
         </is>
       </c>
-      <c r="C15" t="inlineStr">
+      <c r="C21" t="inlineStr">
         <is>
           <t xml:space="preserve">playwright failed: Page.goto: Timeout 25000ms exceeded.
 Call log:
@@ -4428,18 +4600,38 @@
         </is>
       </c>
     </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Amazon India</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>https://www.amazon.jobs/en/locations/india</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">playwright failed: Page.goto: Timeout 25000ms exceeded.
+Call log:
+  - navigating to "https://www.amazon.jobs/en/locations/india", waiting until "networkidle"
+</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
         <is>
           <t>Udaan</t>
         </is>
       </c>
-      <c r="B16" t="inlineStr">
+      <c r="B23" t="inlineStr">
         <is>
           <t>https://udaan.com/careers</t>
         </is>
       </c>
-      <c r="C16" t="inlineStr">
+      <c r="C23" t="inlineStr">
         <is>
           <t xml:space="preserve">playwright failed: Page.goto: Timeout 25000ms exceeded.
 Call log:
@@ -4448,6 +4640,26 @@
         </is>
       </c>
     </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Cigniti Technologies</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>https://www.cigniti.com/careers/</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">playwright failed: Page.goto: Timeout 25000ms exceeded.
+Call log:
+  - navigating to "https://www.cigniti.com/careers/", waiting until "networkidle"
+</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
